--- a/modelo-importacao-capacidade.xlsx
+++ b/modelo-importacao-capacidade.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D084ECA4-B1EC-4BB5-9D24-35B663301BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Capacidade" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instruções" state="visible" r:id="rId5"/>
+    <sheet name="Capacidade" sheetId="1" r:id="rId1"/>
+    <sheet name="Instruções" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="29">
   <si>
     <t>Colaborador</t>
   </si>
@@ -29,24 +33,15 @@
     <t>Horas alocadas</t>
   </si>
   <si>
-    <t>Ana Oliveira</t>
-  </si>
-  <si>
     <t>Desenvolvedor</t>
   </si>
   <si>
     <t>Commerce</t>
   </si>
   <si>
-    <t>Carlos Lima</t>
-  </si>
-  <si>
     <t>Tester</t>
   </si>
   <si>
-    <t>Payments</t>
-  </si>
-  <si>
     <t>Campo</t>
   </si>
   <si>
@@ -75,23 +70,58 @@
   </si>
   <si>
     <t>Alocação base; demandas vinculadas serão adicionadas automaticamente.</t>
+  </si>
+  <si>
+    <t>Anderson</t>
+  </si>
+  <si>
+    <t>Gustavo</t>
+  </si>
+  <si>
+    <t>João Victor</t>
+  </si>
+  <si>
+    <t>João Gabriel</t>
+  </si>
+  <si>
+    <t>Luiz</t>
+  </si>
+  <si>
+    <t>Andrey</t>
+  </si>
+  <si>
+    <t>Guilherme</t>
+  </si>
+  <si>
+    <t>Iohan</t>
+  </si>
+  <si>
+    <t>Bruno Mello</t>
+  </si>
+  <si>
+    <t>Jhonson</t>
+  </si>
+  <si>
+    <t>nddCargo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
@@ -124,12 +154,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,16 +501,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="5" width="20" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="20" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,49 +530,202 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
       <c r="D2">
         <v>130</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>120</v>
-      </c>
-      <c r="E3">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3">
+        <v>130</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3">
+        <v>130</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3">
+        <v>130</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3">
+        <v>130</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3">
+        <v>130</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3">
+        <v>130</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3">
+        <v>130</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3">
+        <v>130</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3">
+        <v>130</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="3">
+        <v>130</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -547,13 +734,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -561,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -572,10 +759,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -583,10 +770,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -594,10 +781,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -605,14 +792,14 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>